--- a/docs/payhome_business_todo.xlsx
+++ b/docs/payhome_business_todo.xlsx
@@ -999,9 +999,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1072,9 +1072,9 @@
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1095,9 +1095,9 @@
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -8232,7 +8232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:V59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8418,13 +8418,13 @@
       <c r="G3" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="13" t="inlineStr"/>
       <c r="K3" s="14" t="inlineStr"/>
@@ -8474,13 +8474,13 @@
       <c r="G4" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="13" t="inlineStr"/>
       <c r="K4" s="13" t="inlineStr"/>
@@ -8530,13 +8530,13 @@
       <c r="G5" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="13" t="inlineStr"/>
       <c r="K5" s="14" t="inlineStr"/>
@@ -8642,13 +8642,13 @@
       <c r="G7" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="13" t="inlineStr"/>
       <c r="K7" s="13" t="inlineStr"/>
@@ -8698,13 +8698,13 @@
       <c r="G8" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
@@ -8754,13 +8754,13 @@
       <c r="G9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="14" t="inlineStr"/>
       <c r="K9" s="13" t="inlineStr"/>
@@ -8866,13 +8866,13 @@
       <c r="G11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="14" t="inlineStr"/>
       <c r="K11" s="13" t="inlineStr"/>
@@ -8922,13 +8922,13 @@
       <c r="G12" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="14" t="inlineStr"/>
       <c r="K12" s="13" t="inlineStr"/>
@@ -9146,13 +9146,13 @@
       <c r="G16" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="14" t="inlineStr"/>
       <c r="K16" s="14" t="inlineStr"/>
@@ -9313,13 +9313,13 @@
       <c r="G19" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="14" t="inlineStr"/>
       <c r="K19" s="14" t="inlineStr"/>
@@ -9478,13 +9478,13 @@
       <c r="G22" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="14" t="inlineStr"/>
       <c r="K22" s="14" t="inlineStr"/>
@@ -9533,13 +9533,13 @@
       <c r="G23" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H23" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="14" t="inlineStr"/>
       <c r="K23" s="14" t="inlineStr"/>
@@ -9705,13 +9705,13 @@
       <c r="G27" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="14" t="inlineStr"/>
       <c r="K27" s="14" t="inlineStr"/>
@@ -9870,13 +9870,13 @@
       <c r="G30" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="14" t="inlineStr"/>
       <c r="K30" s="14" t="inlineStr"/>
@@ -9925,13 +9925,13 @@
       <c r="G31" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="H31" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H31" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="14" t="inlineStr"/>
       <c r="K31" s="14" t="inlineStr"/>
@@ -10090,13 +10090,13 @@
       <c r="G34" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="14" t="inlineStr"/>
       <c r="K34" s="14" t="inlineStr"/>
@@ -10207,13 +10207,13 @@
       <c r="G37" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H37" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="14" t="inlineStr"/>
       <c r="K37" s="14" t="inlineStr"/>
@@ -10317,13 +10317,13 @@
       <c r="G39" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H39" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="14" t="inlineStr"/>
       <c r="K39" s="14" t="inlineStr"/>
@@ -10372,13 +10372,13 @@
       <c r="G40" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H40" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="14" t="inlineStr"/>
       <c r="K40" s="14" t="inlineStr"/>
@@ -10427,13 +10427,13 @@
       <c r="G41" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H41" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="14" t="inlineStr"/>
       <c r="K41" s="14" t="inlineStr"/>
@@ -10482,13 +10482,13 @@
       <c r="G42" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H42" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="14" t="inlineStr"/>
       <c r="K42" s="14" t="inlineStr"/>
@@ -10592,13 +10592,13 @@
       <c r="G44" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H44" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="14" t="inlineStr"/>
       <c r="K44" s="14" t="inlineStr"/>
@@ -10613,6 +10613,21 @@
       <c r="T44" s="13" t="inlineStr"/>
       <c r="U44" s="14" t="inlineStr"/>
     </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A35:U35"/>
@@ -11686,7 +11701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11789,9 +11804,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -11832,9 +11847,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -11918,9 +11933,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -11961,9 +11976,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -12324,9 +12339,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -12464,9 +12479,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -12550,9 +12565,9 @@
           <t>中</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -12604,9 +12619,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -12701,9 +12716,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -12744,9 +12759,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -12787,9 +12802,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -12916,9 +12931,9 @@
           <t>中</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -12963,9 +12978,9 @@
           <t>中</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -13006,9 +13021,9 @@
           <t>中</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -13022,6 +13037,31 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="G2:G60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -13039,7 +13079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13329,13 +13369,13 @@
           <t>05/25</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
@@ -13400,13 +13440,13 @@
           <t>04/07</t>
         </is>
       </c>
-      <c r="K5" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
@@ -13542,13 +13582,13 @@
           <t>03/28</t>
         </is>
       </c>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
@@ -13613,13 +13653,13 @@
           <t>04/04</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K8" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
@@ -13826,13 +13866,13 @@
           <t>04/14</t>
         </is>
       </c>
-      <c r="K11" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
@@ -13897,13 +13937,13 @@
           <t>05/15</t>
         </is>
       </c>
-      <c r="K12" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K12" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
@@ -14181,13 +14221,13 @@
           <t>06/08</t>
         </is>
       </c>
-      <c r="K16" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K16" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
@@ -14252,13 +14292,13 @@
           <t>06/15</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
@@ -14323,13 +14363,13 @@
           <t>04/07</t>
         </is>
       </c>
-      <c r="K18" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
@@ -14394,13 +14434,13 @@
           <t>04/14</t>
         </is>
       </c>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
@@ -14678,13 +14718,13 @@
           <t>04/28</t>
         </is>
       </c>
-      <c r="K23" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
@@ -14749,13 +14789,13 @@
           <t>06/15</t>
         </is>
       </c>
-      <c r="K24" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
@@ -14820,13 +14860,13 @@
           <t>06/08</t>
         </is>
       </c>
-      <c r="K25" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
@@ -14891,13 +14931,13 @@
           <t>03/31</t>
         </is>
       </c>
-      <c r="K26" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
@@ -14962,13 +15002,13 @@
           <t>04/07</t>
         </is>
       </c>
-      <c r="K27" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
@@ -15033,13 +15073,13 @@
           <t>04/07</t>
         </is>
       </c>
-      <c r="K28" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K28" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
@@ -15246,13 +15286,13 @@
           <t>05/02</t>
         </is>
       </c>
-      <c r="K31" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K31" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
@@ -15388,13 +15428,13 @@
           <t>04/04</t>
         </is>
       </c>
-      <c r="K33" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K33" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
@@ -15459,13 +15499,13 @@
           <t>04/21</t>
         </is>
       </c>
-      <c r="K34" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K34" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
@@ -15530,13 +15570,13 @@
           <t>06/08</t>
         </is>
       </c>
-      <c r="K35" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K35" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
@@ -15743,13 +15783,13 @@
           <t>05/09</t>
         </is>
       </c>
-      <c r="K38" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K38" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
@@ -15814,13 +15854,13 @@
           <t>04/21</t>
         </is>
       </c>
-      <c r="K39" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K39" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
@@ -15885,13 +15925,13 @@
           <t>05/11</t>
         </is>
       </c>
-      <c r="K40" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K40" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
@@ -16169,13 +16209,13 @@
           <t>06/22</t>
         </is>
       </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K44" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
@@ -16470,6 +16510,10 @@
       <c r="N55" s="5" t="n"/>
       <c r="O55" s="5" t="inlineStr"/>
     </row>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="K2:K60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -17216,7 +17260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17531,9 +17575,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
